--- a/Result/profitability/4414.xlsx
+++ b/Result/profitability/4414.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.03</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0275</v>
+        <v>-0.009999999999999995</v>
       </c>
       <c r="N2" t="n">
-        <v>18.91875</v>
+        <v>18.74625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.97</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1475</v>
+        <v>-0.1775</v>
       </c>
       <c r="N3" t="n">
-        <v>16.46625</v>
+        <v>16.29375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.52</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.25875</v>
+        <v>-0.24375</v>
       </c>
       <c r="N4" t="n">
-        <v>15.00875</v>
+        <v>14.17</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-3.17</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.65625</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>6.61</v>
+        <v>6.37125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.1</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.56375</v>
+        <v>-0.625</v>
       </c>
       <c r="N6" t="n">
-        <v>5.373749999999999</v>
+        <v>5.2875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.01</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6425</v>
+        <v>-0.70875</v>
       </c>
       <c r="N7" t="n">
-        <v>4.74875</v>
+        <v>4.32375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.42</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7775</v>
+        <v>-0.61125</v>
       </c>
       <c r="N8" t="n">
-        <v>2.72875</v>
+        <v>2.856249999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,10 +1518,10 @@
         <v>-2.04</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8825</v>
+        <v>-0.8825000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.62375</v>
+        <v>-1.623750000000001</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1645,10 +1645,10 @@
         <v>-0.29</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.915</v>
+        <v>-0.9149999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.055</v>
+        <v>-3.055000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>-0.78125</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8387500000000006</v>
+        <v>-0.838750000000001</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1899,10 +1899,10 @@
         <v>0.18</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.69375</v>
+        <v>-0.6937500000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4262499999999991</v>
+        <v>0.4262499999999987</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>-0.28</v>
       </c>
       <c r="N13" t="n">
-        <v>7.39</v>
+        <v>7.389999999999999</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4414</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3845</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3209</v>
+      </c>
+      <c r="E75" t="n">
+        <v>637</v>
+      </c>
+      <c r="F75" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="G75" t="n">
+        <v>28</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.74%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>22</v>
+      </c>
+      <c r="J75" t="n">
+        <v>51</v>
+      </c>
+      <c r="K75" t="n">
+        <v>34</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.007499999999999996</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.36625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.108333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.06563706563706551</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.203125</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1034109366540336</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
